--- a/employee_headcount.xlsx
+++ b/employee_headcount.xlsx
@@ -481,7 +481,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Information Services</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -496,7 +496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Information Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -556,12 +556,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Quality Assurance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Executive General and Administration</t>
+          <t>Quality Assurance</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -571,12 +571,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Production Control</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Executive General and Administration</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -586,12 +586,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quality Assurance</t>
+          <t>Production Control</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quality Assurance</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="C12" t="n">
